--- a/public/2025_2026 Bozo Bets.xlsx
+++ b/public/2025_2026 Bozo Bets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="236">
   <si>
     <t>WK 1</t>
   </si>
@@ -35,15 +35,15 @@
     <t>week 5</t>
   </si>
   <si>
+    <t>Wins/Losses</t>
+  </si>
+  <si>
     <t>week 6</t>
   </si>
   <si>
     <t>week 7</t>
   </si>
   <si>
-    <t>Wins/Losses</t>
-  </si>
-  <si>
     <t>week 8</t>
   </si>
   <si>
@@ -83,15 +83,15 @@
     <t>Week 16</t>
   </si>
   <si>
+    <t>Alabama -13.5</t>
+  </si>
+  <si>
     <t>week 17</t>
   </si>
   <si>
     <t>Xmas Duggie Gift</t>
   </si>
   <si>
-    <t>Alabama -13.5</t>
-  </si>
-  <si>
     <t>Kimmet Sunday Funday</t>
   </si>
   <si>
@@ -101,12 +101,12 @@
     <t>WIns/Losses</t>
   </si>
   <si>
+    <t>Chiefs ML</t>
+  </si>
+  <si>
     <t>Combined W/L</t>
   </si>
   <si>
-    <t>Chiefs ML</t>
-  </si>
-  <si>
     <t>Patriots -3.5</t>
   </si>
   <si>
@@ -116,18 +116,18 @@
     <t>Texans +6.5</t>
   </si>
   <si>
+    <t>Lions +2.5</t>
+  </si>
+  <si>
+    <t>AJ Brown 50 Receiving Yards</t>
+  </si>
+  <si>
     <t>Oklahoma -20.5</t>
   </si>
   <si>
-    <t>Lions +2.5</t>
-  </si>
-  <si>
     <t>James Cook Anytime TD</t>
   </si>
   <si>
-    <t>AJ Brown 50 Receiving Yards</t>
-  </si>
-  <si>
     <t>Texans (of Houston) -5.5</t>
   </si>
   <si>
@@ -137,13 +137,16 @@
     <t>Oregon -6.5</t>
   </si>
   <si>
+    <t>Josh</t>
+  </si>
+  <si>
     <t>Oregon -13.5</t>
   </si>
   <si>
     <t>Alabama -9.5</t>
   </si>
   <si>
-    <t>Josh</t>
+    <t>Ga Tech -3.5</t>
   </si>
   <si>
     <t>49ers +2.5</t>
@@ -152,13 +155,13 @@
     <t>Ravens -2.5</t>
   </si>
   <si>
-    <t>Ga Tech -3.5</t>
+    <t>LSU +4</t>
   </si>
   <si>
     <t>Texas A&amp;M -13.5</t>
   </si>
   <si>
-    <t>LSU +4</t>
+    <t>Den -7</t>
   </si>
   <si>
     <t>Vanderbilt -5.5</t>
@@ -167,18 +170,21 @@
     <t>Eagles -3.5</t>
   </si>
   <si>
-    <t>Den -7</t>
+    <t>Chiefs -2.5</t>
+  </si>
+  <si>
+    <t>Jahmyr Gibbs Anytime TD</t>
+  </si>
+  <si>
+    <t>AJ Brown 5+ Receptions</t>
+  </si>
+  <si>
+    <t>49ers +4.5</t>
   </si>
   <si>
     <t>CLE+8</t>
   </si>
   <si>
-    <t>Chiefs -2.5</t>
-  </si>
-  <si>
-    <t>Jahmyr Gibbs Anytime TD</t>
-  </si>
-  <si>
     <t>Zach</t>
   </si>
   <si>
@@ -194,15 +200,9 @@
     <t>Browns +6.5</t>
   </si>
   <si>
-    <t>AJ Brown 5+ Receptions</t>
-  </si>
-  <si>
     <t>Falcons ML</t>
   </si>
   <si>
-    <t>49ers +4.5</t>
-  </si>
-  <si>
     <t>Giants +7.5</t>
   </si>
   <si>
@@ -326,27 +326,27 @@
     <t>Colts -13.5</t>
   </si>
   <si>
+    <t>Den -7 (-6.5)</t>
+  </si>
+  <si>
     <t>Ravens -5.5</t>
   </si>
   <si>
     <t>Jags +3.5</t>
   </si>
   <si>
-    <t>Den -7 (-6.5)</t>
-  </si>
-  <si>
     <t>Oregon -27</t>
   </si>
   <si>
+    <t>Keon Coleman over 41.5 yards rec</t>
+  </si>
+  <si>
+    <t>PSU -24</t>
+  </si>
+  <si>
     <t>Total Odds</t>
   </si>
   <si>
-    <t>Keon Coleman over 41.5 yards rec</t>
-  </si>
-  <si>
-    <t>PSU -24</t>
-  </si>
-  <si>
     <t>Wager</t>
   </si>
   <si>
@@ -629,82 +629,88 @@
     <t xml:space="preserve">balance </t>
   </si>
   <si>
+    <t>2024/2025</t>
+  </si>
+  <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
     <t>Shane Week 12 Start</t>
   </si>
   <si>
+    <t>22-9</t>
+  </si>
+  <si>
     <t>12-15</t>
   </si>
   <si>
-    <t>22-9</t>
-  </si>
-  <si>
     <t>34-24</t>
   </si>
   <si>
+    <t>17-5</t>
+  </si>
+  <si>
     <t>4-7</t>
   </si>
   <si>
-    <t>17-5</t>
-  </si>
-  <si>
     <t>21-12</t>
   </si>
   <si>
+    <t>14-13</t>
+  </si>
+  <si>
     <t>10-16</t>
   </si>
   <si>
-    <t>14-13</t>
-  </si>
-  <si>
     <t>24-29</t>
   </si>
   <si>
+    <t>13-6</t>
+  </si>
+  <si>
     <t>4-6</t>
   </si>
   <si>
-    <t>13-6</t>
-  </si>
-  <si>
     <t>17-12</t>
   </si>
   <si>
+    <t>18-8</t>
+  </si>
+  <si>
     <t>4-1</t>
   </si>
   <si>
-    <t>18-8</t>
+    <t>23-7</t>
   </si>
   <si>
     <t>17-10</t>
   </si>
   <si>
-    <t>23-7</t>
-  </si>
-  <si>
     <t>40-17</t>
   </si>
   <si>
+    <t>16-14</t>
+  </si>
+  <si>
     <t>17-8</t>
   </si>
   <si>
-    <t>16-14</t>
-  </si>
-  <si>
     <t>33-22</t>
   </si>
   <si>
+    <t>19-10</t>
+  </si>
+  <si>
     <t>12-14</t>
   </si>
   <si>
-    <t>19-10</t>
-  </si>
-  <si>
     <t>31-24</t>
   </si>
   <si>
+    <t>14-6</t>
+  </si>
+  <si>
     <t>16-4</t>
-  </si>
-  <si>
-    <t>14-6</t>
   </si>
   <si>
     <t>30-10</t>
@@ -803,23 +809,23 @@
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1103,10 +1109,10 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>10</v>
@@ -1136,10 +1142,10 @@
         <v>22</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>26</v>
@@ -1152,7 +1158,7 @@
         <v>28</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -1160,16 +1166,16 @@
         <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="7" t="s">
         <v>36</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>38</v>
@@ -1180,49 +1186,49 @@
       <c r="H2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>41</v>
+      <c r="I2" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>45</v>
       </c>
+      <c r="L2" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="M2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="U2" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="12">
+      <c r="W2" s="11">
         <v>46335.0</v>
       </c>
       <c r="X2" s="16" t="str">
@@ -1232,29 +1238,29 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>106</v>
+        <v>41</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -1268,9 +1274,9 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="12">
+        <v>41</v>
+      </c>
+      <c r="W3" s="11">
         <v>46058.0</v>
       </c>
       <c r="X3" s="16" t="str">
@@ -1280,10 +1286,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>114</v>
@@ -1291,57 +1297,57 @@
       <c r="D4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>117</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>118</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>119</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>65</v>
       </c>
       <c r="Q4" s="3"/>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="8" t="s">
         <v>124</v>
       </c>
       <c r="U4" s="4" t="s">
         <v>125</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="W4" s="12">
+        <v>57</v>
+      </c>
+      <c r="W4" s="11">
         <v>46274.0</v>
       </c>
       <c r="X4" s="16" t="str">
@@ -1359,10 +1365,10 @@
       <c r="J5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>128</v>
       </c>
       <c r="M5" s="3"/>
@@ -1370,7 +1376,7 @@
       <c r="O5" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="8" t="s">
         <v>69</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -1383,7 +1389,7 @@
       <c r="V5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="W5" s="12">
+      <c r="W5" s="11">
         <v>46085.0</v>
       </c>
       <c r="X5" s="16" t="str">
@@ -1399,10 +1405,10 @@
       <c r="I6" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>132</v>
       </c>
       <c r="L6" s="3"/>
@@ -1413,14 +1419,14 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="8" t="s">
         <v>133</v>
       </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="W6" s="12">
+      <c r="W6" s="11">
         <v>46082.0</v>
       </c>
       <c r="X6" s="16" t="str">
@@ -1432,7 +1438,7 @@
       <c r="A7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1441,7 +1447,7 @@
       <c r="D7" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -1453,10 +1459,10 @@
       <c r="H7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>78</v>
       </c>
       <c r="K7" s="4" t="s">
@@ -1465,19 +1471,19 @@
       <c r="L7" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="8" t="s">
         <v>141</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="Q7" s="8" t="s">
         <v>143</v>
       </c>
       <c r="R7" s="4" t="s">
@@ -1493,7 +1499,7 @@
       <c r="V7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="11">
         <v>46304.0</v>
       </c>
       <c r="X7" s="16" t="str">
@@ -1505,10 +1511,10 @@
       <c r="A8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>146</v>
       </c>
       <c r="D8" s="6" t="s">
@@ -1526,10 +1532,10 @@
       <c r="H8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>85</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -1541,32 +1547,32 @@
       <c r="M8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="O8" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="8" t="s">
         <v>86</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>157</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="T8" s="7" t="s">
+      <c r="T8" s="8" t="s">
         <v>159</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="12">
+      <c r="W8" s="11">
         <v>46363.0</v>
       </c>
       <c r="X8" s="16" t="str">
@@ -1581,7 +1587,7 @@
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1603,43 +1609,43 @@
         <v>91</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>166</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="8" t="s">
         <v>169</v>
       </c>
       <c r="P9" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="Q9" s="7" t="s">
+      <c r="Q9" s="8" t="s">
         <v>171</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="S9" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="U9" s="8" t="s">
         <v>175</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="W9" s="12">
+      <c r="W9" s="11">
         <v>46304.0</v>
       </c>
       <c r="X9" s="16" t="str">
@@ -1654,7 +1660,7 @@
       <c r="B10" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>177</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -1668,43 +1674,43 @@
       <c r="H10" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="8" t="s">
         <v>182</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="8" t="s">
         <v>97</v>
       </c>
       <c r="Q10" s="3"/>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="8" t="s">
         <v>185</v>
       </c>
       <c r="S10" s="3"/>
-      <c r="T10" s="7" t="s">
+      <c r="T10" s="8" t="s">
         <v>186</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="W10" s="12">
+      <c r="W10" s="11">
         <v>46359.0</v>
       </c>
       <c r="X10" s="16" t="str">
@@ -1716,16 +1722,16 @@
       <c r="A11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>189</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -1740,26 +1746,26 @@
       <c r="I11" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>103</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="8" t="s">
         <v>196</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="P11" s="7" t="s">
-        <v>105</v>
+      <c r="P11" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>198</v>
@@ -1770,16 +1776,16 @@
       <c r="S11" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="T11" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="U11" s="8" t="s">
         <v>201</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="W11" s="12">
+      <c r="W11" s="11">
         <v>46335.0</v>
       </c>
       <c r="X11" s="16" t="str">
@@ -1799,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="13">
         <f>7701</f>
@@ -2023,169 +2029,175 @@
     </row>
     <row r="18">
       <c r="A18" s="17"/>
+      <c r="N18" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="N19" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="O19" s="15" t="s">
         <v>207</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="O19" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="P19" s="15"/>
       <c r="Q19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23">
         <v>70.0</v>
       </c>
-      <c r="N20" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>210</v>
+      <c r="N20" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="O20" s="22" t="s">
+        <v>212</v>
       </c>
       <c r="P20" s="15"/>
       <c r="Q20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17"/>
-      <c r="N21" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="O21" s="15" t="s">
-        <v>213</v>
+      <c r="N21" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="O21" s="22" t="s">
+        <v>215</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R21" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17"/>
-      <c r="N22" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>216</v>
+      <c r="N22" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="O22" s="22" t="s">
+        <v>218</v>
       </c>
       <c r="P22" s="15"/>
       <c r="Q22" s="3" t="s">
         <v>66</v>
       </c>
       <c r="R22" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17"/>
-      <c r="N23" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="O23" s="15" t="s">
-        <v>219</v>
+      <c r="N23" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="O23" s="22" t="s">
+        <v>221</v>
       </c>
       <c r="P23" s="15"/>
       <c r="Q23" s="3" t="s">
         <v>70</v>
       </c>
       <c r="R23" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17"/>
-      <c r="N24" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="O24" s="15" t="s">
-        <v>221</v>
+      <c r="N24" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="O24" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="3" t="s">
         <v>73</v>
       </c>
       <c r="R24" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17"/>
-      <c r="N25" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>224</v>
+      <c r="N25" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="O25" s="22" t="s">
+        <v>226</v>
       </c>
       <c r="P25" s="15"/>
       <c r="Q25" s="3" t="s">
         <v>81</v>
       </c>
       <c r="R25" s="15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17"/>
-      <c r="N26" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>227</v>
+      <c r="N26" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="O26" s="22" t="s">
+        <v>229</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="3" t="s">
         <v>87</v>
       </c>
       <c r="R26" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17"/>
-      <c r="N27" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="O27" s="15" t="s">
-        <v>230</v>
+      <c r="N27" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="O27" s="22" t="s">
+        <v>232</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="3" t="s">
         <v>93</v>
       </c>
       <c r="R27" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17"/>
-      <c r="N28" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="O28" s="15" t="s">
-        <v>232</v>
+      <c r="N28" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="O28" s="22" t="s">
+        <v>234</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="3" t="s">
         <v>98</v>
       </c>
       <c r="R28" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29">
@@ -5142,7 +5154,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M1" s="1"/>
     </row>
@@ -5173,13 +5185,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>31</v>
@@ -5187,12 +5199,12 @@
       <c r="F3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>21</v>
@@ -5203,23 +5215,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K4" s="9">
         <v>46055.0</v>
@@ -5227,24 +5239,24 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>63</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -5254,7 +5266,7 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K5" s="9">
         <v>46029.0</v>
@@ -5264,13 +5276,13 @@
       <c r="A6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="12" t="s">
         <v>67</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -5301,10 +5313,10 @@
       <c r="A8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -5313,7 +5325,7 @@
       <c r="E8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="14" t="s">
@@ -5322,7 +5334,7 @@
       <c r="H8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -5336,10 +5348,10 @@
       <c r="A9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>82</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -5351,7 +5363,7 @@
       <c r="G9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -5380,8 +5392,8 @@
       <c r="F10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>61</v>
+      <c r="G10" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>92</v>
@@ -5403,16 +5415,16 @@
       <c r="E11" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="12" t="s">
         <v>95</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -5426,10 +5438,10 @@
       <c r="A12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -5445,10 +5457,10 @@
         <v>103</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="7" t="s">
         <v>105</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>98</v>
@@ -5462,7 +5474,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B14" s="18">
         <v>4468.0</v>
